--- a/cluster2.xlsx
+++ b/cluster2.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG609"/>
+  <dimension ref="A1:AH609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,6 +595,11 @@
           <t>Total_Promos</t>
         </is>
       </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -696,6 +701,11 @@
       <c r="AG2" t="n">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -797,6 +807,11 @@
       <c r="AG3" t="n">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -898,6 +913,11 @@
       <c r="AG4" t="n">
         <v>0</v>
       </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -999,6 +1019,11 @@
       <c r="AG5" t="n">
         <v>0</v>
       </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1100,6 +1125,11 @@
       <c r="AG6" t="n">
         <v>0</v>
       </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1201,6 +1231,11 @@
       <c r="AG7" t="n">
         <v>0</v>
       </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1302,6 +1337,11 @@
       <c r="AG8" t="n">
         <v>0</v>
       </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1403,6 +1443,11 @@
       <c r="AG9" t="n">
         <v>0</v>
       </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1504,6 +1549,11 @@
       <c r="AG10" t="n">
         <v>0</v>
       </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1605,6 +1655,11 @@
       <c r="AG11" t="n">
         <v>0</v>
       </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1706,6 +1761,11 @@
       <c r="AG12" t="n">
         <v>0</v>
       </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1807,6 +1867,11 @@
       <c r="AG13" t="n">
         <v>0</v>
       </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1908,6 +1973,11 @@
       <c r="AG14" t="n">
         <v>0</v>
       </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2009,6 +2079,11 @@
       <c r="AG15" t="n">
         <v>0</v>
       </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2110,6 +2185,11 @@
       <c r="AG16" t="n">
         <v>0</v>
       </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2211,6 +2291,11 @@
       <c r="AG17" t="n">
         <v>0</v>
       </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2312,6 +2397,11 @@
       <c r="AG18" t="n">
         <v>0</v>
       </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2413,6 +2503,11 @@
       <c r="AG19" t="n">
         <v>0</v>
       </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2514,6 +2609,11 @@
       <c r="AG20" t="n">
         <v>0</v>
       </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2615,6 +2715,11 @@
       <c r="AG21" t="n">
         <v>0</v>
       </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2716,6 +2821,11 @@
       <c r="AG22" t="n">
         <v>0</v>
       </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2817,6 +2927,11 @@
       <c r="AG23" t="n">
         <v>0</v>
       </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2918,6 +3033,11 @@
       <c r="AG24" t="n">
         <v>0</v>
       </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3019,6 +3139,11 @@
       <c r="AG25" t="n">
         <v>0</v>
       </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3120,6 +3245,11 @@
       <c r="AG26" t="n">
         <v>1</v>
       </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3221,6 +3351,11 @@
       <c r="AG27" t="n">
         <v>0</v>
       </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3322,6 +3457,11 @@
       <c r="AG28" t="n">
         <v>0</v>
       </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3423,6 +3563,11 @@
       <c r="AG29" t="n">
         <v>0</v>
       </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3524,6 +3669,11 @@
       <c r="AG30" t="n">
         <v>0</v>
       </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3625,6 +3775,11 @@
       <c r="AG31" t="n">
         <v>0</v>
       </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3726,6 +3881,11 @@
       <c r="AG32" t="n">
         <v>0</v>
       </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3827,6 +3987,11 @@
       <c r="AG33" t="n">
         <v>0</v>
       </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3928,6 +4093,11 @@
       <c r="AG34" t="n">
         <v>0</v>
       </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4029,6 +4199,11 @@
       <c r="AG35" t="n">
         <v>0</v>
       </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4130,6 +4305,11 @@
       <c r="AG36" t="n">
         <v>0</v>
       </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4231,6 +4411,11 @@
       <c r="AG37" t="n">
         <v>0</v>
       </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4332,6 +4517,11 @@
       <c r="AG38" t="n">
         <v>0</v>
       </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4433,6 +4623,11 @@
       <c r="AG39" t="n">
         <v>0</v>
       </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4534,6 +4729,11 @@
       <c r="AG40" t="n">
         <v>0</v>
       </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4635,6 +4835,11 @@
       <c r="AG41" t="n">
         <v>0</v>
       </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4736,6 +4941,11 @@
       <c r="AG42" t="n">
         <v>0</v>
       </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4837,6 +5047,11 @@
       <c r="AG43" t="n">
         <v>0</v>
       </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4938,6 +5153,11 @@
       <c r="AG44" t="n">
         <v>0</v>
       </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5039,6 +5259,11 @@
       <c r="AG45" t="n">
         <v>0</v>
       </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5140,6 +5365,11 @@
       <c r="AG46" t="n">
         <v>0</v>
       </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5241,6 +5471,11 @@
       <c r="AG47" t="n">
         <v>0</v>
       </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5342,6 +5577,11 @@
       <c r="AG48" t="n">
         <v>1</v>
       </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5443,6 +5683,11 @@
       <c r="AG49" t="n">
         <v>0</v>
       </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5544,6 +5789,11 @@
       <c r="AG50" t="n">
         <v>0</v>
       </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5645,6 +5895,11 @@
       <c r="AG51" t="n">
         <v>0</v>
       </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5746,6 +6001,11 @@
       <c r="AG52" t="n">
         <v>0</v>
       </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5847,6 +6107,11 @@
       <c r="AG53" t="n">
         <v>0</v>
       </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5948,6 +6213,11 @@
       <c r="AG54" t="n">
         <v>0</v>
       </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6049,6 +6319,11 @@
       <c r="AG55" t="n">
         <v>1</v>
       </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6150,6 +6425,11 @@
       <c r="AG56" t="n">
         <v>0</v>
       </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6251,6 +6531,11 @@
       <c r="AG57" t="n">
         <v>1</v>
       </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6352,6 +6637,11 @@
       <c r="AG58" t="n">
         <v>1</v>
       </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6453,6 +6743,11 @@
       <c r="AG59" t="n">
         <v>0</v>
       </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6554,6 +6849,11 @@
       <c r="AG60" t="n">
         <v>0</v>
       </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6655,6 +6955,11 @@
       <c r="AG61" t="n">
         <v>0</v>
       </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6756,6 +7061,11 @@
       <c r="AG62" t="n">
         <v>0</v>
       </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6857,6 +7167,11 @@
       <c r="AG63" t="n">
         <v>0</v>
       </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6958,6 +7273,11 @@
       <c r="AG64" t="n">
         <v>0</v>
       </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7059,6 +7379,11 @@
       <c r="AG65" t="n">
         <v>0</v>
       </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7160,6 +7485,11 @@
       <c r="AG66" t="n">
         <v>0</v>
       </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7261,6 +7591,11 @@
       <c r="AG67" t="n">
         <v>0</v>
       </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7362,6 +7697,11 @@
       <c r="AG68" t="n">
         <v>0</v>
       </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7463,6 +7803,11 @@
       <c r="AG69" t="n">
         <v>0</v>
       </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7564,6 +7909,11 @@
       <c r="AG70" t="n">
         <v>0</v>
       </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7665,6 +8015,11 @@
       <c r="AG71" t="n">
         <v>0</v>
       </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7766,6 +8121,11 @@
       <c r="AG72" t="n">
         <v>0</v>
       </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7867,6 +8227,11 @@
       <c r="AG73" t="n">
         <v>1</v>
       </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7968,6 +8333,11 @@
       <c r="AG74" t="n">
         <v>0</v>
       </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8069,6 +8439,11 @@
       <c r="AG75" t="n">
         <v>0</v>
       </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8170,6 +8545,11 @@
       <c r="AG76" t="n">
         <v>0</v>
       </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8271,6 +8651,11 @@
       <c r="AG77" t="n">
         <v>0</v>
       </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8372,6 +8757,11 @@
       <c r="AG78" t="n">
         <v>0</v>
       </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8473,6 +8863,11 @@
       <c r="AG79" t="n">
         <v>0</v>
       </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8574,6 +8969,11 @@
       <c r="AG80" t="n">
         <v>0</v>
       </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8675,6 +9075,11 @@
       <c r="AG81" t="n">
         <v>1</v>
       </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8776,6 +9181,11 @@
       <c r="AG82" t="n">
         <v>0</v>
       </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8877,6 +9287,11 @@
       <c r="AG83" t="n">
         <v>0</v>
       </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8978,6 +9393,11 @@
       <c r="AG84" t="n">
         <v>0</v>
       </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9079,6 +9499,11 @@
       <c r="AG85" t="n">
         <v>0</v>
       </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9180,6 +9605,11 @@
       <c r="AG86" t="n">
         <v>0</v>
       </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9281,6 +9711,11 @@
       <c r="AG87" t="n">
         <v>0</v>
       </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9382,6 +9817,11 @@
       <c r="AG88" t="n">
         <v>0</v>
       </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9483,6 +9923,11 @@
       <c r="AG89" t="n">
         <v>0</v>
       </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9584,6 +10029,11 @@
       <c r="AG90" t="n">
         <v>0</v>
       </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9685,6 +10135,11 @@
       <c r="AG91" t="n">
         <v>0</v>
       </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9786,6 +10241,11 @@
       <c r="AG92" t="n">
         <v>0</v>
       </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9887,6 +10347,11 @@
       <c r="AG93" t="n">
         <v>0</v>
       </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9988,6 +10453,11 @@
       <c r="AG94" t="n">
         <v>0</v>
       </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10089,6 +10559,11 @@
       <c r="AG95" t="n">
         <v>0</v>
       </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10190,6 +10665,11 @@
       <c r="AG96" t="n">
         <v>0</v>
       </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10291,6 +10771,11 @@
       <c r="AG97" t="n">
         <v>0</v>
       </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10392,6 +10877,11 @@
       <c r="AG98" t="n">
         <v>0</v>
       </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10493,6 +10983,11 @@
       <c r="AG99" t="n">
         <v>1</v>
       </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10594,6 +11089,11 @@
       <c r="AG100" t="n">
         <v>0</v>
       </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10695,6 +11195,11 @@
       <c r="AG101" t="n">
         <v>0</v>
       </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10796,6 +11301,11 @@
       <c r="AG102" t="n">
         <v>0</v>
       </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10897,6 +11407,11 @@
       <c r="AG103" t="n">
         <v>1</v>
       </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10998,6 +11513,11 @@
       <c r="AG104" t="n">
         <v>1</v>
       </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11099,6 +11619,11 @@
       <c r="AG105" t="n">
         <v>0</v>
       </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11200,6 +11725,11 @@
       <c r="AG106" t="n">
         <v>0</v>
       </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11301,6 +11831,11 @@
       <c r="AG107" t="n">
         <v>0</v>
       </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11402,6 +11937,11 @@
       <c r="AG108" t="n">
         <v>0</v>
       </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11503,6 +12043,11 @@
       <c r="AG109" t="n">
         <v>0</v>
       </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11604,6 +12149,11 @@
       <c r="AG110" t="n">
         <v>1</v>
       </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11705,6 +12255,11 @@
       <c r="AG111" t="n">
         <v>1</v>
       </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11806,6 +12361,11 @@
       <c r="AG112" t="n">
         <v>0</v>
       </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11907,6 +12467,11 @@
       <c r="AG113" t="n">
         <v>0</v>
       </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12008,6 +12573,11 @@
       <c r="AG114" t="n">
         <v>0</v>
       </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12109,6 +12679,11 @@
       <c r="AG115" t="n">
         <v>0</v>
       </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12210,6 +12785,11 @@
       <c r="AG116" t="n">
         <v>0</v>
       </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12311,6 +12891,11 @@
       <c r="AG117" t="n">
         <v>0</v>
       </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12412,6 +12997,11 @@
       <c r="AG118" t="n">
         <v>0</v>
       </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12513,6 +13103,11 @@
       <c r="AG119" t="n">
         <v>0</v>
       </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12614,6 +13209,11 @@
       <c r="AG120" t="n">
         <v>0</v>
       </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12715,6 +13315,11 @@
       <c r="AG121" t="n">
         <v>0</v>
       </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12816,6 +13421,11 @@
       <c r="AG122" t="n">
         <v>0</v>
       </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12917,6 +13527,11 @@
       <c r="AG123" t="n">
         <v>0</v>
       </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13018,6 +13633,11 @@
       <c r="AG124" t="n">
         <v>0</v>
       </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13119,6 +13739,11 @@
       <c r="AG125" t="n">
         <v>0</v>
       </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13220,6 +13845,11 @@
       <c r="AG126" t="n">
         <v>0</v>
       </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13321,6 +13951,11 @@
       <c r="AG127" t="n">
         <v>1</v>
       </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13422,6 +14057,11 @@
       <c r="AG128" t="n">
         <v>0</v>
       </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13523,6 +14163,11 @@
       <c r="AG129" t="n">
         <v>0</v>
       </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13624,6 +14269,11 @@
       <c r="AG130" t="n">
         <v>0</v>
       </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13725,6 +14375,11 @@
       <c r="AG131" t="n">
         <v>0</v>
       </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13826,6 +14481,11 @@
       <c r="AG132" t="n">
         <v>0</v>
       </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13927,6 +14587,11 @@
       <c r="AG133" t="n">
         <v>0</v>
       </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14028,6 +14693,11 @@
       <c r="AG134" t="n">
         <v>0</v>
       </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14129,6 +14799,11 @@
       <c r="AG135" t="n">
         <v>0</v>
       </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14230,6 +14905,11 @@
       <c r="AG136" t="n">
         <v>0</v>
       </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14331,6 +15011,11 @@
       <c r="AG137" t="n">
         <v>0</v>
       </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14432,6 +15117,11 @@
       <c r="AG138" t="n">
         <v>0</v>
       </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14533,6 +15223,11 @@
       <c r="AG139" t="n">
         <v>0</v>
       </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14634,6 +15329,11 @@
       <c r="AG140" t="n">
         <v>0</v>
       </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14735,6 +15435,11 @@
       <c r="AG141" t="n">
         <v>0</v>
       </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14836,6 +15541,11 @@
       <c r="AG142" t="n">
         <v>0</v>
       </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14937,6 +15647,11 @@
       <c r="AG143" t="n">
         <v>0</v>
       </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15038,6 +15753,11 @@
       <c r="AG144" t="n">
         <v>0</v>
       </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15139,6 +15859,11 @@
       <c r="AG145" t="n">
         <v>0</v>
       </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15240,6 +15965,11 @@
       <c r="AG146" t="n">
         <v>0</v>
       </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15341,6 +16071,11 @@
       <c r="AG147" t="n">
         <v>0</v>
       </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15442,6 +16177,11 @@
       <c r="AG148" t="n">
         <v>1</v>
       </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15543,6 +16283,11 @@
       <c r="AG149" t="n">
         <v>0</v>
       </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15644,6 +16389,11 @@
       <c r="AG150" t="n">
         <v>0</v>
       </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15745,6 +16495,11 @@
       <c r="AG151" t="n">
         <v>0</v>
       </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15846,6 +16601,11 @@
       <c r="AG152" t="n">
         <v>0</v>
       </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15947,6 +16707,11 @@
       <c r="AG153" t="n">
         <v>0</v>
       </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16048,6 +16813,11 @@
       <c r="AG154" t="n">
         <v>1</v>
       </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16149,6 +16919,11 @@
       <c r="AG155" t="n">
         <v>0</v>
       </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16250,6 +17025,11 @@
       <c r="AG156" t="n">
         <v>0</v>
       </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16351,6 +17131,11 @@
       <c r="AG157" t="n">
         <v>0</v>
       </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16452,6 +17237,11 @@
       <c r="AG158" t="n">
         <v>0</v>
       </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16553,6 +17343,11 @@
       <c r="AG159" t="n">
         <v>0</v>
       </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16654,6 +17449,11 @@
       <c r="AG160" t="n">
         <v>0</v>
       </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16755,6 +17555,11 @@
       <c r="AG161" t="n">
         <v>0</v>
       </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16856,6 +17661,11 @@
       <c r="AG162" t="n">
         <v>0</v>
       </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16957,6 +17767,11 @@
       <c r="AG163" t="n">
         <v>0</v>
       </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17058,6 +17873,11 @@
       <c r="AG164" t="n">
         <v>0</v>
       </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17159,6 +17979,11 @@
       <c r="AG165" t="n">
         <v>0</v>
       </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17260,6 +18085,11 @@
       <c r="AG166" t="n">
         <v>0</v>
       </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17361,6 +18191,11 @@
       <c r="AG167" t="n">
         <v>0</v>
       </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17462,6 +18297,11 @@
       <c r="AG168" t="n">
         <v>1</v>
       </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17563,6 +18403,11 @@
       <c r="AG169" t="n">
         <v>0</v>
       </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17664,6 +18509,11 @@
       <c r="AG170" t="n">
         <v>0</v>
       </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17765,6 +18615,11 @@
       <c r="AG171" t="n">
         <v>0</v>
       </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17866,6 +18721,11 @@
       <c r="AG172" t="n">
         <v>0</v>
       </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -17967,6 +18827,11 @@
       <c r="AG173" t="n">
         <v>0</v>
       </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18068,6 +18933,11 @@
       <c r="AG174" t="n">
         <v>0</v>
       </c>
+      <c r="AH174" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18169,6 +19039,11 @@
       <c r="AG175" t="n">
         <v>0</v>
       </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18270,6 +19145,11 @@
       <c r="AG176" t="n">
         <v>0</v>
       </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18371,6 +19251,11 @@
       <c r="AG177" t="n">
         <v>0</v>
       </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18472,6 +19357,11 @@
       <c r="AG178" t="n">
         <v>0</v>
       </c>
+      <c r="AH178" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18573,6 +19463,11 @@
       <c r="AG179" t="n">
         <v>0</v>
       </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18674,6 +19569,11 @@
       <c r="AG180" t="n">
         <v>0</v>
       </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18775,6 +19675,11 @@
       <c r="AG181" t="n">
         <v>0</v>
       </c>
+      <c r="AH181" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -18876,6 +19781,11 @@
       <c r="AG182" t="n">
         <v>0</v>
       </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -18977,6 +19887,11 @@
       <c r="AG183" t="n">
         <v>0</v>
       </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19078,6 +19993,11 @@
       <c r="AG184" t="n">
         <v>0</v>
       </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19179,6 +20099,11 @@
       <c r="AG185" t="n">
         <v>0</v>
       </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19280,6 +20205,11 @@
       <c r="AG186" t="n">
         <v>0</v>
       </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -19381,6 +20311,11 @@
       <c r="AG187" t="n">
         <v>0</v>
       </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -19482,6 +20417,11 @@
       <c r="AG188" t="n">
         <v>0</v>
       </c>
+      <c r="AH188" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -19583,6 +20523,11 @@
       <c r="AG189" t="n">
         <v>0</v>
       </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19684,6 +20629,11 @@
       <c r="AG190" t="n">
         <v>0</v>
       </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19785,6 +20735,11 @@
       <c r="AG191" t="n">
         <v>0</v>
       </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -19886,6 +20841,11 @@
       <c r="AG192" t="n">
         <v>0</v>
       </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -19987,6 +20947,11 @@
       <c r="AG193" t="n">
         <v>0</v>
       </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -20088,6 +21053,11 @@
       <c r="AG194" t="n">
         <v>0</v>
       </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -20189,6 +21159,11 @@
       <c r="AG195" t="n">
         <v>0</v>
       </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -20290,6 +21265,11 @@
       <c r="AG196" t="n">
         <v>0</v>
       </c>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -20391,6 +21371,11 @@
       <c r="AG197" t="n">
         <v>1</v>
       </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -20492,6 +21477,11 @@
       <c r="AG198" t="n">
         <v>0</v>
       </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -20593,6 +21583,11 @@
       <c r="AG199" t="n">
         <v>0</v>
       </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -20694,6 +21689,11 @@
       <c r="AG200" t="n">
         <v>0</v>
       </c>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -20795,6 +21795,11 @@
       <c r="AG201" t="n">
         <v>0</v>
       </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -20896,6 +21901,11 @@
       <c r="AG202" t="n">
         <v>0</v>
       </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -20997,6 +22007,11 @@
       <c r="AG203" t="n">
         <v>0</v>
       </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -21098,6 +22113,11 @@
       <c r="AG204" t="n">
         <v>0</v>
       </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -21199,6 +22219,11 @@
       <c r="AG205" t="n">
         <v>0</v>
       </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -21300,6 +22325,11 @@
       <c r="AG206" t="n">
         <v>0</v>
       </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -21401,6 +22431,11 @@
       <c r="AG207" t="n">
         <v>1</v>
       </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -21502,6 +22537,11 @@
       <c r="AG208" t="n">
         <v>0</v>
       </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -21603,6 +22643,11 @@
       <c r="AG209" t="n">
         <v>0</v>
       </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -21704,6 +22749,11 @@
       <c r="AG210" t="n">
         <v>0</v>
       </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -21805,6 +22855,11 @@
       <c r="AG211" t="n">
         <v>0</v>
       </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -21906,6 +22961,11 @@
       <c r="AG212" t="n">
         <v>0</v>
       </c>
+      <c r="AH212" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -22007,6 +23067,11 @@
       <c r="AG213" t="n">
         <v>1</v>
       </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -22108,6 +23173,11 @@
       <c r="AG214" t="n">
         <v>0</v>
       </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -22209,6 +23279,11 @@
       <c r="AG215" t="n">
         <v>0</v>
       </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -22310,6 +23385,11 @@
       <c r="AG216" t="n">
         <v>0</v>
       </c>
+      <c r="AH216" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -22411,6 +23491,11 @@
       <c r="AG217" t="n">
         <v>0</v>
       </c>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -22512,6 +23597,11 @@
       <c r="AG218" t="n">
         <v>0</v>
       </c>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -22613,6 +23703,11 @@
       <c r="AG219" t="n">
         <v>0</v>
       </c>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -22714,6 +23809,11 @@
       <c r="AG220" t="n">
         <v>0</v>
       </c>
+      <c r="AH220" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -22815,6 +23915,11 @@
       <c r="AG221" t="n">
         <v>1</v>
       </c>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -22916,6 +24021,11 @@
       <c r="AG222" t="n">
         <v>0</v>
       </c>
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -23017,6 +24127,11 @@
       <c r="AG223" t="n">
         <v>0</v>
       </c>
+      <c r="AH223" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -23118,6 +24233,11 @@
       <c r="AG224" t="n">
         <v>0</v>
       </c>
+      <c r="AH224" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -23219,6 +24339,11 @@
       <c r="AG225" t="n">
         <v>0</v>
       </c>
+      <c r="AH225" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -23320,6 +24445,11 @@
       <c r="AG226" t="n">
         <v>1</v>
       </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -23421,6 +24551,11 @@
       <c r="AG227" t="n">
         <v>0</v>
       </c>
+      <c r="AH227" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -23522,6 +24657,11 @@
       <c r="AG228" t="n">
         <v>0</v>
       </c>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -23623,6 +24763,11 @@
       <c r="AG229" t="n">
         <v>1</v>
       </c>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -23724,6 +24869,11 @@
       <c r="AG230" t="n">
         <v>0</v>
       </c>
+      <c r="AH230" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -23825,6 +24975,11 @@
       <c r="AG231" t="n">
         <v>0</v>
       </c>
+      <c r="AH231" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -23926,6 +25081,11 @@
       <c r="AG232" t="n">
         <v>0</v>
       </c>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -24027,6 +25187,11 @@
       <c r="AG233" t="n">
         <v>0</v>
       </c>
+      <c r="AH233" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -24128,6 +25293,11 @@
       <c r="AG234" t="n">
         <v>0</v>
       </c>
+      <c r="AH234" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -24229,6 +25399,11 @@
       <c r="AG235" t="n">
         <v>0</v>
       </c>
+      <c r="AH235" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -24330,6 +25505,11 @@
       <c r="AG236" t="n">
         <v>1</v>
       </c>
+      <c r="AH236" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -24431,6 +25611,11 @@
       <c r="AG237" t="n">
         <v>1</v>
       </c>
+      <c r="AH237" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -24532,6 +25717,11 @@
       <c r="AG238" t="n">
         <v>0</v>
       </c>
+      <c r="AH238" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -24633,6 +25823,11 @@
       <c r="AG239" t="n">
         <v>0</v>
       </c>
+      <c r="AH239" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -24734,6 +25929,11 @@
       <c r="AG240" t="n">
         <v>0</v>
       </c>
+      <c r="AH240" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -24835,6 +26035,11 @@
       <c r="AG241" t="n">
         <v>0</v>
       </c>
+      <c r="AH241" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -24936,6 +26141,11 @@
       <c r="AG242" t="n">
         <v>0</v>
       </c>
+      <c r="AH242" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -25037,6 +26247,11 @@
       <c r="AG243" t="n">
         <v>1</v>
       </c>
+      <c r="AH243" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -25138,6 +26353,11 @@
       <c r="AG244" t="n">
         <v>0</v>
       </c>
+      <c r="AH244" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -25239,6 +26459,11 @@
       <c r="AG245" t="n">
         <v>0</v>
       </c>
+      <c r="AH245" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -25340,6 +26565,11 @@
       <c r="AG246" t="n">
         <v>0</v>
       </c>
+      <c r="AH246" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -25441,6 +26671,11 @@
       <c r="AG247" t="n">
         <v>0</v>
       </c>
+      <c r="AH247" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -25542,6 +26777,11 @@
       <c r="AG248" t="n">
         <v>0</v>
       </c>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -25643,6 +26883,11 @@
       <c r="AG249" t="n">
         <v>0</v>
       </c>
+      <c r="AH249" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -25744,6 +26989,11 @@
       <c r="AG250" t="n">
         <v>0</v>
       </c>
+      <c r="AH250" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -25845,6 +27095,11 @@
       <c r="AG251" t="n">
         <v>0</v>
       </c>
+      <c r="AH251" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -25946,6 +27201,11 @@
       <c r="AG252" t="n">
         <v>0</v>
       </c>
+      <c r="AH252" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -26047,6 +27307,11 @@
       <c r="AG253" t="n">
         <v>0</v>
       </c>
+      <c r="AH253" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -26148,6 +27413,11 @@
       <c r="AG254" t="n">
         <v>0</v>
       </c>
+      <c r="AH254" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -26249,6 +27519,11 @@
       <c r="AG255" t="n">
         <v>0</v>
       </c>
+      <c r="AH255" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -26350,6 +27625,11 @@
       <c r="AG256" t="n">
         <v>0</v>
       </c>
+      <c r="AH256" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -26451,6 +27731,11 @@
       <c r="AG257" t="n">
         <v>0</v>
       </c>
+      <c r="AH257" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -26552,6 +27837,11 @@
       <c r="AG258" t="n">
         <v>0</v>
       </c>
+      <c r="AH258" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -26653,6 +27943,11 @@
       <c r="AG259" t="n">
         <v>1</v>
       </c>
+      <c r="AH259" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -26754,6 +28049,11 @@
       <c r="AG260" t="n">
         <v>0</v>
       </c>
+      <c r="AH260" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -26855,6 +28155,11 @@
       <c r="AG261" t="n">
         <v>0</v>
       </c>
+      <c r="AH261" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -26956,6 +28261,11 @@
       <c r="AG262" t="n">
         <v>1</v>
       </c>
+      <c r="AH262" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -27057,6 +28367,11 @@
       <c r="AG263" t="n">
         <v>0</v>
       </c>
+      <c r="AH263" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -27158,6 +28473,11 @@
       <c r="AG264" t="n">
         <v>0</v>
       </c>
+      <c r="AH264" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -27259,6 +28579,11 @@
       <c r="AG265" t="n">
         <v>0</v>
       </c>
+      <c r="AH265" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -27360,6 +28685,11 @@
       <c r="AG266" t="n">
         <v>0</v>
       </c>
+      <c r="AH266" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -27461,6 +28791,11 @@
       <c r="AG267" t="n">
         <v>0</v>
       </c>
+      <c r="AH267" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -27562,6 +28897,11 @@
       <c r="AG268" t="n">
         <v>0</v>
       </c>
+      <c r="AH268" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -27663,6 +29003,11 @@
       <c r="AG269" t="n">
         <v>0</v>
       </c>
+      <c r="AH269" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -27764,6 +29109,11 @@
       <c r="AG270" t="n">
         <v>0</v>
       </c>
+      <c r="AH270" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -27865,6 +29215,11 @@
       <c r="AG271" t="n">
         <v>0</v>
       </c>
+      <c r="AH271" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -27966,6 +29321,11 @@
       <c r="AG272" t="n">
         <v>0</v>
       </c>
+      <c r="AH272" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -28067,6 +29427,11 @@
       <c r="AG273" t="n">
         <v>0</v>
       </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -28168,6 +29533,11 @@
       <c r="AG274" t="n">
         <v>0</v>
       </c>
+      <c r="AH274" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -28269,6 +29639,11 @@
       <c r="AG275" t="n">
         <v>0</v>
       </c>
+      <c r="AH275" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -28370,6 +29745,11 @@
       <c r="AG276" t="n">
         <v>0</v>
       </c>
+      <c r="AH276" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -28471,6 +29851,11 @@
       <c r="AG277" t="n">
         <v>0</v>
       </c>
+      <c r="AH277" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -28572,6 +29957,11 @@
       <c r="AG278" t="n">
         <v>0</v>
       </c>
+      <c r="AH278" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -28673,6 +30063,11 @@
       <c r="AG279" t="n">
         <v>0</v>
       </c>
+      <c r="AH279" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -28774,6 +30169,11 @@
       <c r="AG280" t="n">
         <v>0</v>
       </c>
+      <c r="AH280" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -28875,6 +30275,11 @@
       <c r="AG281" t="n">
         <v>0</v>
       </c>
+      <c r="AH281" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -28976,6 +30381,11 @@
       <c r="AG282" t="n">
         <v>0</v>
       </c>
+      <c r="AH282" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -29077,6 +30487,11 @@
       <c r="AG283" t="n">
         <v>0</v>
       </c>
+      <c r="AH283" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -29178,6 +30593,11 @@
       <c r="AG284" t="n">
         <v>0</v>
       </c>
+      <c r="AH284" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -29279,6 +30699,11 @@
       <c r="AG285" t="n">
         <v>0</v>
       </c>
+      <c r="AH285" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -29380,6 +30805,11 @@
       <c r="AG286" t="n">
         <v>0</v>
       </c>
+      <c r="AH286" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -29481,6 +30911,11 @@
       <c r="AG287" t="n">
         <v>0</v>
       </c>
+      <c r="AH287" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -29582,6 +31017,11 @@
       <c r="AG288" t="n">
         <v>0</v>
       </c>
+      <c r="AH288" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -29683,6 +31123,11 @@
       <c r="AG289" t="n">
         <v>0</v>
       </c>
+      <c r="AH289" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -29784,6 +31229,11 @@
       <c r="AG290" t="n">
         <v>0</v>
       </c>
+      <c r="AH290" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -29885,6 +31335,11 @@
       <c r="AG291" t="n">
         <v>0</v>
       </c>
+      <c r="AH291" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -29986,6 +31441,11 @@
       <c r="AG292" t="n">
         <v>0</v>
       </c>
+      <c r="AH292" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -30087,6 +31547,11 @@
       <c r="AG293" t="n">
         <v>0</v>
       </c>
+      <c r="AH293" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -30188,6 +31653,11 @@
       <c r="AG294" t="n">
         <v>0</v>
       </c>
+      <c r="AH294" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -30289,6 +31759,11 @@
       <c r="AG295" t="n">
         <v>0</v>
       </c>
+      <c r="AH295" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -30390,6 +31865,11 @@
       <c r="AG296" t="n">
         <v>0</v>
       </c>
+      <c r="AH296" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -30491,6 +31971,11 @@
       <c r="AG297" t="n">
         <v>0</v>
       </c>
+      <c r="AH297" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -30592,6 +32077,11 @@
       <c r="AG298" t="n">
         <v>0</v>
       </c>
+      <c r="AH298" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -30693,6 +32183,11 @@
       <c r="AG299" t="n">
         <v>1</v>
       </c>
+      <c r="AH299" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -30794,6 +32289,11 @@
       <c r="AG300" t="n">
         <v>0</v>
       </c>
+      <c r="AH300" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -30895,6 +32395,11 @@
       <c r="AG301" t="n">
         <v>0</v>
       </c>
+      <c r="AH301" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -30996,6 +32501,11 @@
       <c r="AG302" t="n">
         <v>0</v>
       </c>
+      <c r="AH302" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -31097,6 +32607,11 @@
       <c r="AG303" t="n">
         <v>0</v>
       </c>
+      <c r="AH303" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -31198,6 +32713,11 @@
       <c r="AG304" t="n">
         <v>1</v>
       </c>
+      <c r="AH304" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -31299,6 +32819,11 @@
       <c r="AG305" t="n">
         <v>0</v>
       </c>
+      <c r="AH305" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -31400,6 +32925,11 @@
       <c r="AG306" t="n">
         <v>0</v>
       </c>
+      <c r="AH306" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -31501,6 +33031,11 @@
       <c r="AG307" t="n">
         <v>0</v>
       </c>
+      <c r="AH307" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -31602,6 +33137,11 @@
       <c r="AG308" t="n">
         <v>0</v>
       </c>
+      <c r="AH308" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -31703,6 +33243,11 @@
       <c r="AG309" t="n">
         <v>0</v>
       </c>
+      <c r="AH309" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -31804,6 +33349,11 @@
       <c r="AG310" t="n">
         <v>0</v>
       </c>
+      <c r="AH310" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -31905,6 +33455,11 @@
       <c r="AG311" t="n">
         <v>0</v>
       </c>
+      <c r="AH311" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -32006,6 +33561,11 @@
       <c r="AG312" t="n">
         <v>0</v>
       </c>
+      <c r="AH312" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -32107,6 +33667,11 @@
       <c r="AG313" t="n">
         <v>0</v>
       </c>
+      <c r="AH313" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -32208,6 +33773,11 @@
       <c r="AG314" t="n">
         <v>0</v>
       </c>
+      <c r="AH314" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -32309,6 +33879,11 @@
       <c r="AG315" t="n">
         <v>0</v>
       </c>
+      <c r="AH315" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -32410,6 +33985,11 @@
       <c r="AG316" t="n">
         <v>0</v>
       </c>
+      <c r="AH316" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -32511,6 +34091,11 @@
       <c r="AG317" t="n">
         <v>0</v>
       </c>
+      <c r="AH317" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -32612,6 +34197,11 @@
       <c r="AG318" t="n">
         <v>0</v>
       </c>
+      <c r="AH318" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -32713,6 +34303,11 @@
       <c r="AG319" t="n">
         <v>0</v>
       </c>
+      <c r="AH319" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -32814,6 +34409,11 @@
       <c r="AG320" t="n">
         <v>0</v>
       </c>
+      <c r="AH320" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -32915,6 +34515,11 @@
       <c r="AG321" t="n">
         <v>0</v>
       </c>
+      <c r="AH321" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -33016,6 +34621,11 @@
       <c r="AG322" t="n">
         <v>0</v>
       </c>
+      <c r="AH322" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -33117,6 +34727,11 @@
       <c r="AG323" t="n">
         <v>1</v>
       </c>
+      <c r="AH323" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -33218,6 +34833,11 @@
       <c r="AG324" t="n">
         <v>1</v>
       </c>
+      <c r="AH324" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -33319,6 +34939,11 @@
       <c r="AG325" t="n">
         <v>0</v>
       </c>
+      <c r="AH325" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -33420,6 +35045,11 @@
       <c r="AG326" t="n">
         <v>0</v>
       </c>
+      <c r="AH326" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -33521,6 +35151,11 @@
       <c r="AG327" t="n">
         <v>0</v>
       </c>
+      <c r="AH327" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -33622,6 +35257,11 @@
       <c r="AG328" t="n">
         <v>0</v>
       </c>
+      <c r="AH328" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -33723,6 +35363,11 @@
       <c r="AG329" t="n">
         <v>0</v>
       </c>
+      <c r="AH329" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -33824,6 +35469,11 @@
       <c r="AG330" t="n">
         <v>0</v>
       </c>
+      <c r="AH330" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -33925,6 +35575,11 @@
       <c r="AG331" t="n">
         <v>0</v>
       </c>
+      <c r="AH331" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -34026,6 +35681,11 @@
       <c r="AG332" t="n">
         <v>0</v>
       </c>
+      <c r="AH332" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -34127,6 +35787,11 @@
       <c r="AG333" t="n">
         <v>0</v>
       </c>
+      <c r="AH333" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -34228,6 +35893,11 @@
       <c r="AG334" t="n">
         <v>0</v>
       </c>
+      <c r="AH334" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -34329,6 +35999,11 @@
       <c r="AG335" t="n">
         <v>0</v>
       </c>
+      <c r="AH335" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -34430,6 +36105,11 @@
       <c r="AG336" t="n">
         <v>1</v>
       </c>
+      <c r="AH336" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -34531,6 +36211,11 @@
       <c r="AG337" t="n">
         <v>1</v>
       </c>
+      <c r="AH337" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -34632,6 +36317,11 @@
       <c r="AG338" t="n">
         <v>0</v>
       </c>
+      <c r="AH338" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -34733,6 +36423,11 @@
       <c r="AG339" t="n">
         <v>1</v>
       </c>
+      <c r="AH339" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -34834,6 +36529,11 @@
       <c r="AG340" t="n">
         <v>0</v>
       </c>
+      <c r="AH340" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -34935,6 +36635,11 @@
       <c r="AG341" t="n">
         <v>0</v>
       </c>
+      <c r="AH341" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -35036,6 +36741,11 @@
       <c r="AG342" t="n">
         <v>0</v>
       </c>
+      <c r="AH342" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -35137,6 +36847,11 @@
       <c r="AG343" t="n">
         <v>0</v>
       </c>
+      <c r="AH343" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -35238,6 +36953,11 @@
       <c r="AG344" t="n">
         <v>1</v>
       </c>
+      <c r="AH344" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -35339,6 +37059,11 @@
       <c r="AG345" t="n">
         <v>0</v>
       </c>
+      <c r="AH345" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -35440,6 +37165,11 @@
       <c r="AG346" t="n">
         <v>0</v>
       </c>
+      <c r="AH346" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -35541,6 +37271,11 @@
       <c r="AG347" t="n">
         <v>0</v>
       </c>
+      <c r="AH347" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -35642,6 +37377,11 @@
       <c r="AG348" t="n">
         <v>1</v>
       </c>
+      <c r="AH348" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -35743,6 +37483,11 @@
       <c r="AG349" t="n">
         <v>0</v>
       </c>
+      <c r="AH349" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -35844,6 +37589,11 @@
       <c r="AG350" t="n">
         <v>0</v>
       </c>
+      <c r="AH350" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -35945,6 +37695,11 @@
       <c r="AG351" t="n">
         <v>0</v>
       </c>
+      <c r="AH351" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -36046,6 +37801,11 @@
       <c r="AG352" t="n">
         <v>0</v>
       </c>
+      <c r="AH352" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -36147,6 +37907,11 @@
       <c r="AG353" t="n">
         <v>0</v>
       </c>
+      <c r="AH353" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -36248,6 +38013,11 @@
       <c r="AG354" t="n">
         <v>0</v>
       </c>
+      <c r="AH354" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -36349,6 +38119,11 @@
       <c r="AG355" t="n">
         <v>0</v>
       </c>
+      <c r="AH355" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -36450,6 +38225,11 @@
       <c r="AG356" t="n">
         <v>0</v>
       </c>
+      <c r="AH356" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -36551,6 +38331,11 @@
       <c r="AG357" t="n">
         <v>0</v>
       </c>
+      <c r="AH357" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -36652,6 +38437,11 @@
       <c r="AG358" t="n">
         <v>1</v>
       </c>
+      <c r="AH358" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -36753,6 +38543,11 @@
       <c r="AG359" t="n">
         <v>0</v>
       </c>
+      <c r="AH359" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -36854,6 +38649,11 @@
       <c r="AG360" t="n">
         <v>1</v>
       </c>
+      <c r="AH360" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -36955,6 +38755,11 @@
       <c r="AG361" t="n">
         <v>0</v>
       </c>
+      <c r="AH361" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -37056,6 +38861,11 @@
       <c r="AG362" t="n">
         <v>0</v>
       </c>
+      <c r="AH362" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -37157,6 +38967,11 @@
       <c r="AG363" t="n">
         <v>0</v>
       </c>
+      <c r="AH363" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -37258,6 +39073,11 @@
       <c r="AG364" t="n">
         <v>0</v>
       </c>
+      <c r="AH364" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -37359,6 +39179,11 @@
       <c r="AG365" t="n">
         <v>0</v>
       </c>
+      <c r="AH365" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -37460,6 +39285,11 @@
       <c r="AG366" t="n">
         <v>0</v>
       </c>
+      <c r="AH366" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -37561,6 +39391,11 @@
       <c r="AG367" t="n">
         <v>0</v>
       </c>
+      <c r="AH367" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -37662,6 +39497,11 @@
       <c r="AG368" t="n">
         <v>0</v>
       </c>
+      <c r="AH368" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -37763,6 +39603,11 @@
       <c r="AG369" t="n">
         <v>0</v>
       </c>
+      <c r="AH369" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -37864,6 +39709,11 @@
       <c r="AG370" t="n">
         <v>0</v>
       </c>
+      <c r="AH370" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -37965,6 +39815,11 @@
       <c r="AG371" t="n">
         <v>0</v>
       </c>
+      <c r="AH371" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -38066,6 +39921,11 @@
       <c r="AG372" t="n">
         <v>0</v>
       </c>
+      <c r="AH372" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -38167,6 +40027,11 @@
       <c r="AG373" t="n">
         <v>0</v>
       </c>
+      <c r="AH373" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -38268,6 +40133,11 @@
       <c r="AG374" t="n">
         <v>0</v>
       </c>
+      <c r="AH374" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -38369,6 +40239,11 @@
       <c r="AG375" t="n">
         <v>0</v>
       </c>
+      <c r="AH375" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -38470,6 +40345,11 @@
       <c r="AG376" t="n">
         <v>0</v>
       </c>
+      <c r="AH376" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -38571,6 +40451,11 @@
       <c r="AG377" t="n">
         <v>0</v>
       </c>
+      <c r="AH377" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -38672,6 +40557,11 @@
       <c r="AG378" t="n">
         <v>0</v>
       </c>
+      <c r="AH378" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -38773,6 +40663,11 @@
       <c r="AG379" t="n">
         <v>0</v>
       </c>
+      <c r="AH379" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -38874,6 +40769,11 @@
       <c r="AG380" t="n">
         <v>0</v>
       </c>
+      <c r="AH380" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -38975,6 +40875,11 @@
       <c r="AG381" t="n">
         <v>0</v>
       </c>
+      <c r="AH381" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -39076,6 +40981,11 @@
       <c r="AG382" t="n">
         <v>0</v>
       </c>
+      <c r="AH382" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -39177,6 +41087,11 @@
       <c r="AG383" t="n">
         <v>0</v>
       </c>
+      <c r="AH383" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -39278,6 +41193,11 @@
       <c r="AG384" t="n">
         <v>1</v>
       </c>
+      <c r="AH384" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -39379,6 +41299,11 @@
       <c r="AG385" t="n">
         <v>1</v>
       </c>
+      <c r="AH385" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -39480,6 +41405,11 @@
       <c r="AG386" t="n">
         <v>0</v>
       </c>
+      <c r="AH386" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -39581,6 +41511,11 @@
       <c r="AG387" t="n">
         <v>0</v>
       </c>
+      <c r="AH387" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -39682,6 +41617,11 @@
       <c r="AG388" t="n">
         <v>1</v>
       </c>
+      <c r="AH388" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -39783,6 +41723,11 @@
       <c r="AG389" t="n">
         <v>0</v>
       </c>
+      <c r="AH389" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -39884,6 +41829,11 @@
       <c r="AG390" t="n">
         <v>0</v>
       </c>
+      <c r="AH390" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -39985,6 +41935,11 @@
       <c r="AG391" t="n">
         <v>0</v>
       </c>
+      <c r="AH391" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -40086,6 +42041,11 @@
       <c r="AG392" t="n">
         <v>0</v>
       </c>
+      <c r="AH392" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -40187,6 +42147,11 @@
       <c r="AG393" t="n">
         <v>0</v>
       </c>
+      <c r="AH393" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -40288,6 +42253,11 @@
       <c r="AG394" t="n">
         <v>0</v>
       </c>
+      <c r="AH394" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -40389,6 +42359,11 @@
       <c r="AG395" t="n">
         <v>0</v>
       </c>
+      <c r="AH395" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -40490,6 +42465,11 @@
       <c r="AG396" t="n">
         <v>0</v>
       </c>
+      <c r="AH396" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -40591,6 +42571,11 @@
       <c r="AG397" t="n">
         <v>0</v>
       </c>
+      <c r="AH397" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -40692,6 +42677,11 @@
       <c r="AG398" t="n">
         <v>0</v>
       </c>
+      <c r="AH398" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -40793,6 +42783,11 @@
       <c r="AG399" t="n">
         <v>0</v>
       </c>
+      <c r="AH399" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -40894,6 +42889,11 @@
       <c r="AG400" t="n">
         <v>0</v>
       </c>
+      <c r="AH400" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -40995,6 +42995,11 @@
       <c r="AG401" t="n">
         <v>0</v>
       </c>
+      <c r="AH401" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -41096,6 +43101,11 @@
       <c r="AG402" t="n">
         <v>0</v>
       </c>
+      <c r="AH402" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -41197,6 +43207,11 @@
       <c r="AG403" t="n">
         <v>0</v>
       </c>
+      <c r="AH403" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -41298,6 +43313,11 @@
       <c r="AG404" t="n">
         <v>0</v>
       </c>
+      <c r="AH404" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -41399,6 +43419,11 @@
       <c r="AG405" t="n">
         <v>0</v>
       </c>
+      <c r="AH405" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -41500,6 +43525,11 @@
       <c r="AG406" t="n">
         <v>0</v>
       </c>
+      <c r="AH406" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -41601,6 +43631,11 @@
       <c r="AG407" t="n">
         <v>0</v>
       </c>
+      <c r="AH407" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -41702,6 +43737,11 @@
       <c r="AG408" t="n">
         <v>0</v>
       </c>
+      <c r="AH408" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -41803,6 +43843,11 @@
       <c r="AG409" t="n">
         <v>0</v>
       </c>
+      <c r="AH409" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -41904,6 +43949,11 @@
       <c r="AG410" t="n">
         <v>0</v>
       </c>
+      <c r="AH410" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -42005,6 +44055,11 @@
       <c r="AG411" t="n">
         <v>0</v>
       </c>
+      <c r="AH411" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -42106,6 +44161,11 @@
       <c r="AG412" t="n">
         <v>0</v>
       </c>
+      <c r="AH412" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -42207,6 +44267,11 @@
       <c r="AG413" t="n">
         <v>0</v>
       </c>
+      <c r="AH413" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -42308,6 +44373,11 @@
       <c r="AG414" t="n">
         <v>0</v>
       </c>
+      <c r="AH414" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -42409,6 +44479,11 @@
       <c r="AG415" t="n">
         <v>0</v>
       </c>
+      <c r="AH415" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -42510,6 +44585,11 @@
       <c r="AG416" t="n">
         <v>0</v>
       </c>
+      <c r="AH416" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -42611,6 +44691,11 @@
       <c r="AG417" t="n">
         <v>0</v>
       </c>
+      <c r="AH417" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -42712,6 +44797,11 @@
       <c r="AG418" t="n">
         <v>0</v>
       </c>
+      <c r="AH418" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -42813,6 +44903,11 @@
       <c r="AG419" t="n">
         <v>0</v>
       </c>
+      <c r="AH419" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -42914,6 +45009,11 @@
       <c r="AG420" t="n">
         <v>0</v>
       </c>
+      <c r="AH420" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -43015,6 +45115,11 @@
       <c r="AG421" t="n">
         <v>0</v>
       </c>
+      <c r="AH421" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -43116,6 +45221,11 @@
       <c r="AG422" t="n">
         <v>0</v>
       </c>
+      <c r="AH422" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -43217,6 +45327,11 @@
       <c r="AG423" t="n">
         <v>0</v>
       </c>
+      <c r="AH423" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -43318,6 +45433,11 @@
       <c r="AG424" t="n">
         <v>1</v>
       </c>
+      <c r="AH424" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -43419,6 +45539,11 @@
       <c r="AG425" t="n">
         <v>0</v>
       </c>
+      <c r="AH425" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -43520,6 +45645,11 @@
       <c r="AG426" t="n">
         <v>0</v>
       </c>
+      <c r="AH426" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -43621,6 +45751,11 @@
       <c r="AG427" t="n">
         <v>0</v>
       </c>
+      <c r="AH427" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -43722,6 +45857,11 @@
       <c r="AG428" t="n">
         <v>0</v>
       </c>
+      <c r="AH428" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -43823,6 +45963,11 @@
       <c r="AG429" t="n">
         <v>0</v>
       </c>
+      <c r="AH429" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -43924,6 +46069,11 @@
       <c r="AG430" t="n">
         <v>0</v>
       </c>
+      <c r="AH430" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -44025,6 +46175,11 @@
       <c r="AG431" t="n">
         <v>0</v>
       </c>
+      <c r="AH431" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -44126,6 +46281,11 @@
       <c r="AG432" t="n">
         <v>0</v>
       </c>
+      <c r="AH432" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -44227,6 +46387,11 @@
       <c r="AG433" t="n">
         <v>0</v>
       </c>
+      <c r="AH433" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -44328,6 +46493,11 @@
       <c r="AG434" t="n">
         <v>0</v>
       </c>
+      <c r="AH434" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -44429,6 +46599,11 @@
       <c r="AG435" t="n">
         <v>0</v>
       </c>
+      <c r="AH435" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -44530,6 +46705,11 @@
       <c r="AG436" t="n">
         <v>0</v>
       </c>
+      <c r="AH436" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -44631,6 +46811,11 @@
       <c r="AG437" t="n">
         <v>0</v>
       </c>
+      <c r="AH437" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -44732,6 +46917,11 @@
       <c r="AG438" t="n">
         <v>0</v>
       </c>
+      <c r="AH438" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -44833,6 +47023,11 @@
       <c r="AG439" t="n">
         <v>0</v>
       </c>
+      <c r="AH439" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -44934,6 +47129,11 @@
       <c r="AG440" t="n">
         <v>0</v>
       </c>
+      <c r="AH440" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -45035,6 +47235,11 @@
       <c r="AG441" t="n">
         <v>0</v>
       </c>
+      <c r="AH441" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -45136,6 +47341,11 @@
       <c r="AG442" t="n">
         <v>0</v>
       </c>
+      <c r="AH442" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -45237,6 +47447,11 @@
       <c r="AG443" t="n">
         <v>0</v>
       </c>
+      <c r="AH443" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -45338,6 +47553,11 @@
       <c r="AG444" t="n">
         <v>0</v>
       </c>
+      <c r="AH444" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -45439,6 +47659,11 @@
       <c r="AG445" t="n">
         <v>0</v>
       </c>
+      <c r="AH445" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -45540,6 +47765,11 @@
       <c r="AG446" t="n">
         <v>0</v>
       </c>
+      <c r="AH446" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -45641,6 +47871,11 @@
       <c r="AG447" t="n">
         <v>1</v>
       </c>
+      <c r="AH447" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -45742,6 +47977,11 @@
       <c r="AG448" t="n">
         <v>0</v>
       </c>
+      <c r="AH448" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -45843,6 +48083,11 @@
       <c r="AG449" t="n">
         <v>0</v>
       </c>
+      <c r="AH449" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -45944,6 +48189,11 @@
       <c r="AG450" t="n">
         <v>0</v>
       </c>
+      <c r="AH450" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -46045,6 +48295,11 @@
       <c r="AG451" t="n">
         <v>0</v>
       </c>
+      <c r="AH451" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -46146,6 +48401,11 @@
       <c r="AG452" t="n">
         <v>0</v>
       </c>
+      <c r="AH452" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -46247,6 +48507,11 @@
       <c r="AG453" t="n">
         <v>0</v>
       </c>
+      <c r="AH453" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -46348,6 +48613,11 @@
       <c r="AG454" t="n">
         <v>0</v>
       </c>
+      <c r="AH454" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -46449,6 +48719,11 @@
       <c r="AG455" t="n">
         <v>0</v>
       </c>
+      <c r="AH455" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -46550,6 +48825,11 @@
       <c r="AG456" t="n">
         <v>0</v>
       </c>
+      <c r="AH456" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -46651,6 +48931,11 @@
       <c r="AG457" t="n">
         <v>0</v>
       </c>
+      <c r="AH457" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -46752,6 +49037,11 @@
       <c r="AG458" t="n">
         <v>0</v>
       </c>
+      <c r="AH458" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -46853,6 +49143,11 @@
       <c r="AG459" t="n">
         <v>0</v>
       </c>
+      <c r="AH459" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -46954,6 +49249,11 @@
       <c r="AG460" t="n">
         <v>0</v>
       </c>
+      <c r="AH460" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -47055,6 +49355,11 @@
       <c r="AG461" t="n">
         <v>0</v>
       </c>
+      <c r="AH461" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -47156,6 +49461,11 @@
       <c r="AG462" t="n">
         <v>0</v>
       </c>
+      <c r="AH462" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -47257,6 +49567,11 @@
       <c r="AG463" t="n">
         <v>2</v>
       </c>
+      <c r="AH463" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -47358,6 +49673,11 @@
       <c r="AG464" t="n">
         <v>0</v>
       </c>
+      <c r="AH464" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -47459,6 +49779,11 @@
       <c r="AG465" t="n">
         <v>0</v>
       </c>
+      <c r="AH465" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -47560,6 +49885,11 @@
       <c r="AG466" t="n">
         <v>0</v>
       </c>
+      <c r="AH466" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -47661,6 +49991,11 @@
       <c r="AG467" t="n">
         <v>0</v>
       </c>
+      <c r="AH467" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -47762,6 +50097,11 @@
       <c r="AG468" t="n">
         <v>0</v>
       </c>
+      <c r="AH468" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -47863,6 +50203,11 @@
       <c r="AG469" t="n">
         <v>0</v>
       </c>
+      <c r="AH469" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -47964,6 +50309,11 @@
       <c r="AG470" t="n">
         <v>0</v>
       </c>
+      <c r="AH470" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -48065,6 +50415,11 @@
       <c r="AG471" t="n">
         <v>0</v>
       </c>
+      <c r="AH471" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -48166,6 +50521,11 @@
       <c r="AG472" t="n">
         <v>0</v>
       </c>
+      <c r="AH472" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -48267,6 +50627,11 @@
       <c r="AG473" t="n">
         <v>0</v>
       </c>
+      <c r="AH473" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -48368,6 +50733,11 @@
       <c r="AG474" t="n">
         <v>0</v>
       </c>
+      <c r="AH474" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -48469,6 +50839,11 @@
       <c r="AG475" t="n">
         <v>0</v>
       </c>
+      <c r="AH475" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -48570,6 +50945,11 @@
       <c r="AG476" t="n">
         <v>0</v>
       </c>
+      <c r="AH476" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -48671,6 +51051,11 @@
       <c r="AG477" t="n">
         <v>0</v>
       </c>
+      <c r="AH477" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -48772,6 +51157,11 @@
       <c r="AG478" t="n">
         <v>0</v>
       </c>
+      <c r="AH478" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -48873,6 +51263,11 @@
       <c r="AG479" t="n">
         <v>0</v>
       </c>
+      <c r="AH479" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -48974,6 +51369,11 @@
       <c r="AG480" t="n">
         <v>0</v>
       </c>
+      <c r="AH480" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -49075,6 +51475,11 @@
       <c r="AG481" t="n">
         <v>0</v>
       </c>
+      <c r="AH481" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -49176,6 +51581,11 @@
       <c r="AG482" t="n">
         <v>0</v>
       </c>
+      <c r="AH482" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -49277,6 +51687,11 @@
       <c r="AG483" t="n">
         <v>0</v>
       </c>
+      <c r="AH483" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -49378,6 +51793,11 @@
       <c r="AG484" t="n">
         <v>0</v>
       </c>
+      <c r="AH484" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -49479,6 +51899,11 @@
       <c r="AG485" t="n">
         <v>0</v>
       </c>
+      <c r="AH485" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -49580,6 +52005,11 @@
       <c r="AG486" t="n">
         <v>0</v>
       </c>
+      <c r="AH486" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -49681,6 +52111,11 @@
       <c r="AG487" t="n">
         <v>0</v>
       </c>
+      <c r="AH487" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -49782,6 +52217,11 @@
       <c r="AG488" t="n">
         <v>0</v>
       </c>
+      <c r="AH488" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -49883,6 +52323,11 @@
       <c r="AG489" t="n">
         <v>0</v>
       </c>
+      <c r="AH489" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -49984,6 +52429,11 @@
       <c r="AG490" t="n">
         <v>0</v>
       </c>
+      <c r="AH490" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -50085,6 +52535,11 @@
       <c r="AG491" t="n">
         <v>0</v>
       </c>
+      <c r="AH491" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -50186,6 +52641,11 @@
       <c r="AG492" t="n">
         <v>0</v>
       </c>
+      <c r="AH492" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -50287,6 +52747,11 @@
       <c r="AG493" t="n">
         <v>0</v>
       </c>
+      <c r="AH493" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -50388,6 +52853,11 @@
       <c r="AG494" t="n">
         <v>0</v>
       </c>
+      <c r="AH494" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -50489,6 +52959,11 @@
       <c r="AG495" t="n">
         <v>0</v>
       </c>
+      <c r="AH495" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -50590,6 +53065,11 @@
       <c r="AG496" t="n">
         <v>0</v>
       </c>
+      <c r="AH496" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -50691,6 +53171,11 @@
       <c r="AG497" t="n">
         <v>0</v>
       </c>
+      <c r="AH497" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -50792,6 +53277,11 @@
       <c r="AG498" t="n">
         <v>0</v>
       </c>
+      <c r="AH498" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -50893,6 +53383,11 @@
       <c r="AG499" t="n">
         <v>0</v>
       </c>
+      <c r="AH499" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -50994,6 +53489,11 @@
       <c r="AG500" t="n">
         <v>0</v>
       </c>
+      <c r="AH500" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -51095,6 +53595,11 @@
       <c r="AG501" t="n">
         <v>0</v>
       </c>
+      <c r="AH501" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -51196,6 +53701,11 @@
       <c r="AG502" t="n">
         <v>0</v>
       </c>
+      <c r="AH502" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -51297,6 +53807,11 @@
       <c r="AG503" t="n">
         <v>0</v>
       </c>
+      <c r="AH503" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -51398,6 +53913,11 @@
       <c r="AG504" t="n">
         <v>0</v>
       </c>
+      <c r="AH504" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -51499,6 +54019,11 @@
       <c r="AG505" t="n">
         <v>0</v>
       </c>
+      <c r="AH505" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -51600,6 +54125,11 @@
       <c r="AG506" t="n">
         <v>0</v>
       </c>
+      <c r="AH506" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -51701,6 +54231,11 @@
       <c r="AG507" t="n">
         <v>0</v>
       </c>
+      <c r="AH507" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -51802,6 +54337,11 @@
       <c r="AG508" t="n">
         <v>0</v>
       </c>
+      <c r="AH508" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -51903,6 +54443,11 @@
       <c r="AG509" t="n">
         <v>0</v>
       </c>
+      <c r="AH509" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -52004,6 +54549,11 @@
       <c r="AG510" t="n">
         <v>0</v>
       </c>
+      <c r="AH510" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -52105,6 +54655,11 @@
       <c r="AG511" t="n">
         <v>0</v>
       </c>
+      <c r="AH511" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -52206,6 +54761,11 @@
       <c r="AG512" t="n">
         <v>0</v>
       </c>
+      <c r="AH512" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -52307,6 +54867,11 @@
       <c r="AG513" t="n">
         <v>0</v>
       </c>
+      <c r="AH513" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -52408,6 +54973,11 @@
       <c r="AG514" t="n">
         <v>0</v>
       </c>
+      <c r="AH514" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -52509,6 +55079,11 @@
       <c r="AG515" t="n">
         <v>1</v>
       </c>
+      <c r="AH515" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -52610,6 +55185,11 @@
       <c r="AG516" t="n">
         <v>0</v>
       </c>
+      <c r="AH516" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -52711,6 +55291,11 @@
       <c r="AG517" t="n">
         <v>0</v>
       </c>
+      <c r="AH517" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -52812,6 +55397,11 @@
       <c r="AG518" t="n">
         <v>0</v>
       </c>
+      <c r="AH518" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -52913,6 +55503,11 @@
       <c r="AG519" t="n">
         <v>1</v>
       </c>
+      <c r="AH519" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -53014,6 +55609,11 @@
       <c r="AG520" t="n">
         <v>0</v>
       </c>
+      <c r="AH520" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -53115,6 +55715,11 @@
       <c r="AG521" t="n">
         <v>0</v>
       </c>
+      <c r="AH521" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -53216,6 +55821,11 @@
       <c r="AG522" t="n">
         <v>0</v>
       </c>
+      <c r="AH522" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -53317,6 +55927,11 @@
       <c r="AG523" t="n">
         <v>0</v>
       </c>
+      <c r="AH523" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -53418,6 +56033,11 @@
       <c r="AG524" t="n">
         <v>0</v>
       </c>
+      <c r="AH524" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -53519,6 +56139,11 @@
       <c r="AG525" t="n">
         <v>1</v>
       </c>
+      <c r="AH525" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -53620,6 +56245,11 @@
       <c r="AG526" t="n">
         <v>0</v>
       </c>
+      <c r="AH526" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -53721,6 +56351,11 @@
       <c r="AG527" t="n">
         <v>0</v>
       </c>
+      <c r="AH527" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -53822,6 +56457,11 @@
       <c r="AG528" t="n">
         <v>0</v>
       </c>
+      <c r="AH528" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -53923,6 +56563,11 @@
       <c r="AG529" t="n">
         <v>0</v>
       </c>
+      <c r="AH529" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -54024,6 +56669,11 @@
       <c r="AG530" t="n">
         <v>0</v>
       </c>
+      <c r="AH530" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -54125,6 +56775,11 @@
       <c r="AG531" t="n">
         <v>0</v>
       </c>
+      <c r="AH531" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -54226,6 +56881,11 @@
       <c r="AG532" t="n">
         <v>0</v>
       </c>
+      <c r="AH532" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -54327,6 +56987,11 @@
       <c r="AG533" t="n">
         <v>0</v>
       </c>
+      <c r="AH533" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -54428,6 +57093,11 @@
       <c r="AG534" t="n">
         <v>0</v>
       </c>
+      <c r="AH534" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -54529,6 +57199,11 @@
       <c r="AG535" t="n">
         <v>0</v>
       </c>
+      <c r="AH535" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -54630,6 +57305,11 @@
       <c r="AG536" t="n">
         <v>0</v>
       </c>
+      <c r="AH536" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -54731,6 +57411,11 @@
       <c r="AG537" t="n">
         <v>0</v>
       </c>
+      <c r="AH537" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -54832,6 +57517,11 @@
       <c r="AG538" t="n">
         <v>1</v>
       </c>
+      <c r="AH538" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -54933,6 +57623,11 @@
       <c r="AG539" t="n">
         <v>0</v>
       </c>
+      <c r="AH539" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -55034,6 +57729,11 @@
       <c r="AG540" t="n">
         <v>1</v>
       </c>
+      <c r="AH540" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -55135,6 +57835,11 @@
       <c r="AG541" t="n">
         <v>0</v>
       </c>
+      <c r="AH541" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
@@ -55236,6 +57941,11 @@
       <c r="AG542" t="n">
         <v>0</v>
       </c>
+      <c r="AH542" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
@@ -55337,6 +58047,11 @@
       <c r="AG543" t="n">
         <v>0</v>
       </c>
+      <c r="AH543" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
@@ -55438,6 +58153,11 @@
       <c r="AG544" t="n">
         <v>0</v>
       </c>
+      <c r="AH544" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -55539,6 +58259,11 @@
       <c r="AG545" t="n">
         <v>0</v>
       </c>
+      <c r="AH545" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
@@ -55640,6 +58365,11 @@
       <c r="AG546" t="n">
         <v>0</v>
       </c>
+      <c r="AH546" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="n">
@@ -55741,6 +58471,11 @@
       <c r="AG547" t="n">
         <v>0</v>
       </c>
+      <c r="AH547" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
@@ -55842,6 +58577,11 @@
       <c r="AG548" t="n">
         <v>0</v>
       </c>
+      <c r="AH548" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
@@ -55943,6 +58683,11 @@
       <c r="AG549" t="n">
         <v>0</v>
       </c>
+      <c r="AH549" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
@@ -56044,6 +58789,11 @@
       <c r="AG550" t="n">
         <v>0</v>
       </c>
+      <c r="AH550" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
@@ -56145,6 +58895,11 @@
       <c r="AG551" t="n">
         <v>0</v>
       </c>
+      <c r="AH551" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
@@ -56246,6 +59001,11 @@
       <c r="AG552" t="n">
         <v>0</v>
       </c>
+      <c r="AH552" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
@@ -56347,6 +59107,11 @@
       <c r="AG553" t="n">
         <v>0</v>
       </c>
+      <c r="AH553" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
@@ -56448,6 +59213,11 @@
       <c r="AG554" t="n">
         <v>0</v>
       </c>
+      <c r="AH554" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
@@ -56549,6 +59319,11 @@
       <c r="AG555" t="n">
         <v>0</v>
       </c>
+      <c r="AH555" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
@@ -56650,6 +59425,11 @@
       <c r="AG556" t="n">
         <v>0</v>
       </c>
+      <c r="AH556" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
@@ -56751,6 +59531,11 @@
       <c r="AG557" t="n">
         <v>0</v>
       </c>
+      <c r="AH557" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
@@ -56852,6 +59637,11 @@
       <c r="AG558" t="n">
         <v>0</v>
       </c>
+      <c r="AH558" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
@@ -56953,6 +59743,11 @@
       <c r="AG559" t="n">
         <v>0</v>
       </c>
+      <c r="AH559" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="n">
@@ -57054,6 +59849,11 @@
       <c r="AG560" t="n">
         <v>0</v>
       </c>
+      <c r="AH560" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="n">
@@ -57155,6 +59955,11 @@
       <c r="AG561" t="n">
         <v>0</v>
       </c>
+      <c r="AH561" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
@@ -57256,6 +60061,11 @@
       <c r="AG562" t="n">
         <v>0</v>
       </c>
+      <c r="AH562" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
@@ -57357,6 +60167,11 @@
       <c r="AG563" t="n">
         <v>0</v>
       </c>
+      <c r="AH563" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
@@ -57458,6 +60273,11 @@
       <c r="AG564" t="n">
         <v>0</v>
       </c>
+      <c r="AH564" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
@@ -57559,6 +60379,11 @@
       <c r="AG565" t="n">
         <v>0</v>
       </c>
+      <c r="AH565" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
@@ -57660,6 +60485,11 @@
       <c r="AG566" t="n">
         <v>0</v>
       </c>
+      <c r="AH566" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
@@ -57761,6 +60591,11 @@
       <c r="AG567" t="n">
         <v>0</v>
       </c>
+      <c r="AH567" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
@@ -57862,6 +60697,11 @@
       <c r="AG568" t="n">
         <v>0</v>
       </c>
+      <c r="AH568" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
@@ -57963,6 +60803,11 @@
       <c r="AG569" t="n">
         <v>0</v>
       </c>
+      <c r="AH569" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
@@ -58064,6 +60909,11 @@
       <c r="AG570" t="n">
         <v>0</v>
       </c>
+      <c r="AH570" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
@@ -58165,6 +61015,11 @@
       <c r="AG571" t="n">
         <v>0</v>
       </c>
+      <c r="AH571" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
@@ -58266,6 +61121,11 @@
       <c r="AG572" t="n">
         <v>0</v>
       </c>
+      <c r="AH572" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
@@ -58367,6 +61227,11 @@
       <c r="AG573" t="n">
         <v>0</v>
       </c>
+      <c r="AH573" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
@@ -58468,6 +61333,11 @@
       <c r="AG574" t="n">
         <v>0</v>
       </c>
+      <c r="AH574" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
@@ -58569,6 +61439,11 @@
       <c r="AG575" t="n">
         <v>0</v>
       </c>
+      <c r="AH575" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
@@ -58670,6 +61545,11 @@
       <c r="AG576" t="n">
         <v>0</v>
       </c>
+      <c r="AH576" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
@@ -58771,6 +61651,11 @@
       <c r="AG577" t="n">
         <v>0</v>
       </c>
+      <c r="AH577" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="n">
@@ -58872,6 +61757,11 @@
       <c r="AG578" t="n">
         <v>0</v>
       </c>
+      <c r="AH578" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="n">
@@ -58973,6 +61863,11 @@
       <c r="AG579" t="n">
         <v>0</v>
       </c>
+      <c r="AH579" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
@@ -59074,6 +61969,11 @@
       <c r="AG580" t="n">
         <v>0</v>
       </c>
+      <c r="AH580" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="n">
@@ -59175,6 +62075,11 @@
       <c r="AG581" t="n">
         <v>0</v>
       </c>
+      <c r="AH581" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
@@ -59276,6 +62181,11 @@
       <c r="AG582" t="n">
         <v>0</v>
       </c>
+      <c r="AH582" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="n">
@@ -59377,6 +62287,11 @@
       <c r="AG583" t="n">
         <v>0</v>
       </c>
+      <c r="AH583" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
@@ -59478,6 +62393,11 @@
       <c r="AG584" t="n">
         <v>0</v>
       </c>
+      <c r="AH584" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
@@ -59579,6 +62499,11 @@
       <c r="AG585" t="n">
         <v>0</v>
       </c>
+      <c r="AH585" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="n">
@@ -59680,6 +62605,11 @@
       <c r="AG586" t="n">
         <v>0</v>
       </c>
+      <c r="AH586" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
@@ -59781,6 +62711,11 @@
       <c r="AG587" t="n">
         <v>0</v>
       </c>
+      <c r="AH587" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="n">
@@ -59882,6 +62817,11 @@
       <c r="AG588" t="n">
         <v>0</v>
       </c>
+      <c r="AH588" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="n">
@@ -59983,6 +62923,11 @@
       <c r="AG589" t="n">
         <v>0</v>
       </c>
+      <c r="AH589" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
@@ -60084,6 +63029,11 @@
       <c r="AG590" t="n">
         <v>0</v>
       </c>
+      <c r="AH590" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="n">
@@ -60185,6 +63135,11 @@
       <c r="AG591" t="n">
         <v>0</v>
       </c>
+      <c r="AH591" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="n">
@@ -60286,6 +63241,11 @@
       <c r="AG592" t="n">
         <v>0</v>
       </c>
+      <c r="AH592" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="n">
@@ -60387,6 +63347,11 @@
       <c r="AG593" t="n">
         <v>0</v>
       </c>
+      <c r="AH593" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="n">
@@ -60488,6 +63453,11 @@
       <c r="AG594" t="n">
         <v>0</v>
       </c>
+      <c r="AH594" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="n">
@@ -60589,6 +63559,11 @@
       <c r="AG595" t="n">
         <v>0</v>
       </c>
+      <c r="AH595" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="n">
@@ -60690,6 +63665,11 @@
       <c r="AG596" t="n">
         <v>0</v>
       </c>
+      <c r="AH596" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="n">
@@ -60791,6 +63771,11 @@
       <c r="AG597" t="n">
         <v>0</v>
       </c>
+      <c r="AH597" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="n">
@@ -60892,6 +63877,11 @@
       <c r="AG598" t="n">
         <v>0</v>
       </c>
+      <c r="AH598" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="n">
@@ -60993,6 +63983,11 @@
       <c r="AG599" t="n">
         <v>0</v>
       </c>
+      <c r="AH599" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="n">
@@ -61094,6 +64089,11 @@
       <c r="AG600" t="n">
         <v>0</v>
       </c>
+      <c r="AH600" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="n">
@@ -61195,6 +64195,11 @@
       <c r="AG601" t="n">
         <v>0</v>
       </c>
+      <c r="AH601" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="n">
@@ -61296,6 +64301,11 @@
       <c r="AG602" t="n">
         <v>0</v>
       </c>
+      <c r="AH602" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
@@ -61397,6 +64407,11 @@
       <c r="AG603" t="n">
         <v>0</v>
       </c>
+      <c r="AH603" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="n">
@@ -61498,6 +64513,11 @@
       <c r="AG604" t="n">
         <v>0</v>
       </c>
+      <c r="AH604" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="n">
@@ -61599,6 +64619,11 @@
       <c r="AG605" t="n">
         <v>0</v>
       </c>
+      <c r="AH605" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="n">
@@ -61700,6 +64725,11 @@
       <c r="AG606" t="n">
         <v>0</v>
       </c>
+      <c r="AH606" t="inlineStr">
+        <is>
+          <t>doanhnlb23411@st.uel.edu.vn</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="n">
@@ -61801,6 +64831,11 @@
       <c r="AG607" t="n">
         <v>1</v>
       </c>
+      <c r="AH607" t="inlineStr">
+        <is>
+          <t>huyn61777@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="n">
@@ -61902,6 +64937,11 @@
       <c r="AG608" t="n">
         <v>0</v>
       </c>
+      <c r="AH608" t="inlineStr">
+        <is>
+          <t>lamthuydung.chntmka62020@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="n">
@@ -62002,6 +65042,11 @@
       </c>
       <c r="AG609" t="n">
         <v>0</v>
+      </c>
+      <c r="AH609" t="inlineStr">
+        <is>
+          <t>hongngocmocay@gmail.com</t>
+        </is>
       </c>
     </row>
   </sheetData>
